--- a/lawyer_forms/014_karnes_county_grand_jury_district_court_juror_questionnaire--lawyer_forms.xlsx
+++ b/lawyer_forms/014_karnes_county_grand_jury_district_court_juror_questionnaire--lawyer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'name',_'label':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'name', 'label': 'Name', 'type': 'text', 'required': True}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'address',_'label':_'address',_'type':_'text'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'address', 'label': 'Address', 'type': 'text'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'city',_'label':_'city',_'type':_'text'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'city', 'label': 'City', 'type': 'text'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'state',_'label':_'state',_'type':_'text'}</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'state', 'label': 'State', 'type': 'text'}</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'zip',_'label':_'zip',_'type':_'text'}</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'zip', 'label': 'Zip', 'type': 'text'}</t>
+          <t>Zip</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'work_phone',_'label':_'work_phone',_'type':_'text',_'required':_true}</t>
+          <t>work_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'work_phone', 'label': 'Work Phone', 'type': 'text', 'required': True}</t>
+          <t>Work Phone</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'home_phone',_'label':_'home_phone',_'type':_'text',_'required':_true}</t>
+          <t>home_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'home_phone', 'label': 'Home Phone', 'type': 'text', 'required': True}</t>
+          <t>Home Phone</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cell_phone',_'label':_'cell_phone',_'type':_'text',_'required':_true}</t>
+          <t>cell_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cell_phone', 'label': 'Cell Phone', 'type': 'text', 'required': True}</t>
+          <t>Cell Phone</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'email',_'label':_'email',_'type':_'email',_'required':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'email', 'label': 'Email', 'type': 'email', 'required': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other',_'label':_'other',_'type':_'text',_'required':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other', 'label': 'Other', 'type': 'text', 'required': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'have_previous_experience',_'label':_'do_you_have_previous_experience_as_a_juror?',_'type':_'select_one',_'options':_[1,_2,_3]}</t>
+          <t>do_you_have_previous_experience_as_a_juror?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'have_previous_experience', 'label': 'Do you have previous experience as a juror?', 'type': 'select_one', 'options': [1, 2, 3]}</t>
+          <t>Do you have previous experience as a juror?</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'have_completed_other_jury_trials',_'label':_'how_many_jury_trials_have_you_completed_in_the_past_year?',_'type':_'select_one',_'options':_[1,_2,_3]}</t>
+          <t>how_many_jury_trials_have_you_completed_in_the_past_year?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'have_completed_other_jury_trials', 'label': 'How many jury trials have you completed in the past year?', 'type': 'select_one', 'options': [1, 2, 3]}</t>
+          <t>How many jury trials have you completed in the past year?</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'number_of_years_as_juror',_'label':_'how_many_years_have_you_served_as_a_juror?',_'type':_'select_one',_'options':_[1,_2,_3]}</t>
+          <t>how_many_years_have_you_served_as_a_juror?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'number_of_years_as_juror', 'label': 'How many years have you served as a juror?', 'type': 'select_one', 'options': [1, 2, 3]}</t>
+          <t>How many years have you served as a juror?</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'served_as_juror',_'label':_'have_you_served_as_a_juror_in_any_other_courts_besides_the_district_court?',_'type':_'select_one',_'options':_[1,_2,_3]}</t>
+          <t>have_you_served_as_a_juror_in_any_other_courts_besides_the_district_court?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'served_as_juror', 'label': 'Have you served as a juror in any other courts besides the district court?', 'type': 'select_one', 'options': [1, 2, 3]}</t>
+          <t>Have you served as a juror in any other courts besides the district court?</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'have_juror_fee',_'label':_'do_you_have_been_paid_any_fee_for_serving_as_a_juror?',_'type':_'select_one',_'options':_[1,_2,_3]}</t>
+          <t>do_you_have_been_paid_any_fee_for_serving_as_a_juror?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'have_juror_fee', 'label': 'Do you have been paid any fee for serving as a juror?', 'type': 'select_one', 'options': [1, 2, 3]}</t>
+          <t>Do you have been paid any fee for serving as a juror?</t>
         </is>
       </c>
     </row>
